--- a/Sample_run/1/student/nguyendvhe176752/TC6/GradeDetail.xlsx
+++ b/Sample_run/1/student/nguyendvhe176752/TC6/GradeDetail.xlsx
@@ -206,16 +206,16 @@
     <x:t>Client closing connection</x:t>
   </x:si>
   <x:si>
+    <x:t>S111</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"StudentId":"S111","Name":null,"Major":null,"Year":null,"GPA":null,"Status":"error","Message":"Student not found"}</x:t>
+  </x:si>
+  <x:si>
     <x:t>(MISSING - not captured)</x:t>
   </x:si>
   <x:si>
     <x:t>FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>S111</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{"StudentId":"S111","Name":null,"Major":null,"Year":null,"GPA":null,"Status":"error","Message":"Student not found"}</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1104,7 +1104,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>35886</x:v>
+        <x:v>45450</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1163,7 +1163,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>35886</x:v>
+        <x:v>45450</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>48</x:v>
@@ -1216,7 +1216,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>35886</x:v>
+        <x:v>45450</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1272,7 +1272,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>35886</x:v>
+        <x:v>45450</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1331,7 +1331,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q6" s="0">
-        <x:v>35886</x:v>
+        <x:v>45450</x:v>
       </x:c>
       <x:c r="R6" s="2" t="s">
         <x:v>48</x:v>
@@ -1387,7 +1387,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q7" s="0">
-        <x:v>35886</x:v>
+        <x:v>45450</x:v>
       </x:c>
       <x:c r="R7" s="2" t="s">
         <x:v>48</x:v>
@@ -1440,7 +1440,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="0">
-        <x:v>35886</x:v>
+        <x:v>45450</x:v>
       </x:c>
       <x:c r="Q8" s="0">
         <x:v>4000</x:v>
@@ -1499,7 +1499,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>35886</x:v>
+        <x:v>45450</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>60</x:v>
@@ -1543,22 +1543,22 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="M10" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="N10" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O10" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="0">
+        <x:v>45450</x:v>
+      </x:c>
+      <x:c r="Q10" s="0">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="Q10" s="0">
-        <x:v>35886</x:v>
-      </x:c>
-      <x:c r="R10" s="2" t="s">
-        <x:v>48</x:v>
+      <x:c r="R10" s="3" t="s">
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:18">
@@ -1608,7 +1608,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="0">
-        <x:v>35886</x:v>
+        <x:v>45450</x:v>
       </x:c>
       <x:c r="Q11" s="0">
         <x:v>4000</x:v>
@@ -1649,28 +1649,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L12" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="M12" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="N12" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="O12" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="R12" s="4" t="s">
-        <x:v>63</x:v>
+      <x:c r="P12" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q12" s="0">
+        <x:v>45450</x:v>
+      </x:c>
+      <x:c r="R12" s="3" t="s">
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:18">
@@ -1720,7 +1720,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P13" s="0">
-        <x:v>54170</x:v>
+        <x:v>41734</x:v>
       </x:c>
       <x:c r="Q13" s="0">
         <x:v>4000</x:v>
@@ -1779,7 +1779,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q14" s="0">
-        <x:v>54170</x:v>
+        <x:v>41734</x:v>
       </x:c>
       <x:c r="R14" s="2" t="s">
         <x:v>48</x:v>
@@ -1832,7 +1832,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P15" s="0">
-        <x:v>54170</x:v>
+        <x:v>41734</x:v>
       </x:c>
       <x:c r="Q15" s="0">
         <x:v>4000</x:v>
@@ -1864,7 +1864,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="H16" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="I16" s="0" t="s">
         <x:v>46</x:v>
@@ -1885,10 +1885,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="O16" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="P16" s="0">
-        <x:v>54170</x:v>
+        <x:v>41734</x:v>
       </x:c>
       <x:c r="Q16" s="0">
         <x:v>4000</x:v>
@@ -1947,7 +1947,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q17" s="0">
-        <x:v>54170</x:v>
+        <x:v>41734</x:v>
       </x:c>
       <x:c r="R17" s="2" t="s">
         <x:v>48</x:v>
@@ -1976,7 +1976,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="H18" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="I18" s="0" t="s">
         <x:v>47</x:v>
@@ -1997,13 +1997,13 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="O18" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="P18" s="0">
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q18" s="0">
-        <x:v>54170</x:v>
+        <x:v>41734</x:v>
       </x:c>
       <x:c r="R18" s="2" t="s">
         <x:v>48</x:v>
@@ -2056,7 +2056,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P19" s="0">
-        <x:v>54170</x:v>
+        <x:v>41734</x:v>
       </x:c>
       <x:c r="Q19" s="0">
         <x:v>4000</x:v>
@@ -2115,7 +2115,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q20" s="0">
-        <x:v>54170</x:v>
+        <x:v>41734</x:v>
       </x:c>
       <x:c r="R20" s="3" t="s">
         <x:v>60</x:v>
@@ -2159,22 +2159,22 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="M21" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="N21" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="O21" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="P21" s="0">
-        <x:v>54170</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q21" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="R21" s="3" t="s">
-        <x:v>60</x:v>
+        <x:v>41734</x:v>
+      </x:c>
+      <x:c r="R21" s="2" t="s">
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:18">
@@ -2224,7 +2224,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P22" s="0">
-        <x:v>54170</x:v>
+        <x:v>41734</x:v>
       </x:c>
       <x:c r="Q22" s="0">
         <x:v>4000</x:v>
@@ -2265,28 +2265,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K23" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="L23" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M23" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N23" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O23" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P23" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q23" s="0">
-        <x:v>54170</x:v>
-      </x:c>
-      <x:c r="R23" s="3" t="s">
-        <x:v>60</x:v>
+      <x:c r="P23" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q23" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R23" s="4" t="s">
+        <x:v>65</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
